--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,67 +565,67 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>34.8975</v>
+        <v>34.6902</v>
       </c>
       <c r="E2" t="n">
-        <v>35.6724</v>
+        <v>34.7346</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7749000000000003</v>
+        <v>-0.04469999999999974</v>
       </c>
       <c r="G2" t="n">
-        <v>11.2062</v>
+        <v>11.0841</v>
       </c>
       <c r="H2" t="n">
-        <v>10.1967</v>
+        <v>10.074</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0095</v>
+        <v>1.0101</v>
       </c>
       <c r="J2" t="n">
-        <v>19.4154</v>
+        <v>18.9759</v>
       </c>
       <c r="K2" t="n">
-        <v>11.7876</v>
+        <v>11.4696</v>
       </c>
       <c r="L2" t="n">
-        <v>7.6278</v>
+        <v>7.5063</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.209199999999999</v>
+        <v>-7.8921</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5912</v>
+        <v>-1.3962</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.6183</v>
+        <v>-6.4962</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0769</v>
+        <v>2.0985</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.9228</v>
+        <v>-6.9948</v>
       </c>
       <c r="R2" t="n">
-        <v>8.999400000000001</v>
+        <v>9.0936</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5825</v>
+        <v>4.674</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8625</v>
+        <v>0.7056</v>
       </c>
       <c r="U2" t="n">
-        <v>3.72</v>
+        <v>3.9687</v>
       </c>
       <c r="V2" t="n">
-        <v>17.0322</v>
+        <v>16.8336</v>
       </c>
       <c r="W2" t="n">
-        <v>22.3173</v>
+        <v>22.0485</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.2851</v>
+        <v>-5.2149</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>27.1647</v>
+        <v>27.1182</v>
       </c>
       <c r="E3" t="n">
-        <v>32.9172</v>
+        <v>32.0802</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.7525</v>
+        <v>-4.9617</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.7591</v>
+        <v>-2.8452</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1163</v>
+        <v>0.9728999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.8757</v>
+        <v>-3.8181</v>
       </c>
       <c r="J3" t="n">
-        <v>10.7949</v>
+        <v>10.3641</v>
       </c>
       <c r="K3" t="n">
-        <v>5.739000000000001</v>
+        <v>5.3949</v>
       </c>
       <c r="L3" t="n">
-        <v>5.0559</v>
+        <v>4.9695</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.5546</v>
+        <v>-13.209</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.6227</v>
+        <v>-4.4217</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.9316</v>
+        <v>-8.787599999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>11.0763</v>
+        <v>11.1921</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>11.0763</v>
+        <v>11.1921</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3086</v>
+        <v>4.362299999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6821999999999999</v>
+        <v>0.4911</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6264</v>
+        <v>3.8712</v>
       </c>
       <c r="V3" t="n">
-        <v>14.5395</v>
+        <v>14.409</v>
       </c>
       <c r="W3" t="n">
-        <v>21.4398</v>
+        <v>21.225</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.9006</v>
+        <v>-6.816</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>24.0957</v>
+        <v>23.8812</v>
       </c>
       <c r="E4" t="n">
-        <v>30.5694</v>
+        <v>29.2488</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.4734</v>
+        <v>-5.367599999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.894999999999998</v>
+        <v>5.693700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>23.0904</v>
+        <v>22.791</v>
       </c>
       <c r="I4" t="n">
-        <v>-17.1954</v>
+        <v>-17.0973</v>
       </c>
       <c r="J4" t="n">
-        <v>29.6568</v>
+        <v>28.9242</v>
       </c>
       <c r="K4" t="n">
-        <v>29.2683</v>
+        <v>28.6635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3882000000000003</v>
+        <v>0.2601</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.7615</v>
+        <v>-23.2302</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.178199999999999</v>
+        <v>-5.8728</v>
       </c>
       <c r="O4" t="n">
-        <v>-17.5833</v>
+        <v>-17.3574</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6924</v>
+        <v>0.6996</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.1529</v>
+        <v>-13.2906</v>
       </c>
       <c r="R4" t="n">
-        <v>13.8453</v>
+        <v>13.9899</v>
       </c>
       <c r="S4" t="n">
-        <v>5.7615</v>
+        <v>5.8692</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2645999999999999</v>
+        <v>-0.01619999999999988</v>
       </c>
       <c r="U4" t="n">
-        <v>5.4969</v>
+        <v>5.8854</v>
       </c>
       <c r="V4" t="n">
-        <v>11.7471</v>
+        <v>11.6187</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8009</v>
+        <v>13.6317</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0541</v>
+        <v>-2.013</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>11.2701</v>
+        <v>11.4582</v>
       </c>
       <c r="E5" t="n">
-        <v>19.8867</v>
+        <v>19.4517</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.6166</v>
+        <v>-7.9938</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2134</v>
+        <v>5.234999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>8.327400000000001</v>
+        <v>8.3361</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1143</v>
+        <v>-3.1011</v>
       </c>
       <c r="J5" t="n">
-        <v>8.777699999999999</v>
+        <v>8.571899999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>9.9009</v>
+        <v>9.759599999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1232</v>
+        <v>-1.1877</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5643</v>
+        <v>-3.3369</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5732</v>
+        <v>-1.4235</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9908</v>
+        <v>-1.9134</v>
       </c>
       <c r="P5" t="n">
-        <v>4.8462</v>
+        <v>4.896599999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8462</v>
+        <v>4.896599999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4418</v>
+        <v>4.5285</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9774</v>
+        <v>0.8616</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4644</v>
+        <v>3.6666</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
       <c r="W5" t="n">
-        <v>10.1316</v>
+        <v>10.0179</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.3623</v>
+        <v>-13.2198</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>10.7745</v>
+        <v>10.7358</v>
       </c>
       <c r="E6" t="n">
-        <v>14.3046</v>
+        <v>13.6926</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.5301</v>
+        <v>-2.9571</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5166</v>
+        <v>6.3609</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5399</v>
+        <v>10.3143</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.023</v>
+        <v>-3.9534</v>
       </c>
       <c r="J6" t="n">
-        <v>10.5798</v>
+        <v>10.212</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5829</v>
+        <v>9.221400000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9906</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.0632</v>
+        <v>-3.8511</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9567</v>
+        <v>1.0929</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.0199</v>
+        <v>-4.9437</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6924</v>
+        <v>0.6996</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8462</v>
+        <v>-4.896599999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>5.538</v>
+        <v>5.5959</v>
       </c>
       <c r="S6" t="n">
-        <v>5.181</v>
+        <v>5.2764</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6701</v>
+        <v>1.5615</v>
       </c>
       <c r="U6" t="n">
-        <v>3.5109</v>
+        <v>3.7152</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6155</v>
+        <v>-1.6008</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9006</v>
+        <v>6.816</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.5161</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10.2717</v>
+        <v>10.3077</v>
       </c>
       <c r="E7" t="n">
-        <v>12.5433</v>
+        <v>12.2652</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2716</v>
+        <v>-1.9575</v>
       </c>
       <c r="G7" t="n">
-        <v>11.1378</v>
+        <v>11.0805</v>
       </c>
       <c r="H7" t="n">
-        <v>6.176699999999999</v>
+        <v>6.1338</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9611</v>
+        <v>4.9467</v>
       </c>
       <c r="J7" t="n">
-        <v>14.292</v>
+        <v>14.0832</v>
       </c>
       <c r="K7" t="n">
-        <v>7.7322</v>
+        <v>7.5846</v>
       </c>
       <c r="L7" t="n">
-        <v>6.5595</v>
+        <v>6.4986</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1542</v>
+        <v>-3.0033</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5555</v>
+        <v>-1.4511</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5984</v>
+        <v>-1.5519</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3848</v>
+        <v>1.3992</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3845</v>
+        <v>-1.3989</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7693</v>
+        <v>2.7981</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9807</v>
+        <v>1.0308</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3639</v>
+        <v>-0.4191</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3446</v>
+        <v>1.4496</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.231</v>
+        <v>-3.2019</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>6.502799999999999</v>
+        <v>6.6849</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8029</v>
+        <v>2.459399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6999</v>
+        <v>4.2258</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.419600000000001</v>
+        <v>-4.3347</v>
       </c>
       <c r="H8" t="n">
-        <v>1.302299999999999</v>
+        <v>1.3287</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.7225</v>
+        <v>-5.6634</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9659</v>
+        <v>1.7943</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3641</v>
+        <v>1.2327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6014999999999996</v>
+        <v>0.5619000000000003</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.385800000000001</v>
+        <v>-6.1287</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06179999999999986</v>
+        <v>0.09659999999999991</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.324</v>
+        <v>-6.2253</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1538</v>
+        <v>4.1973</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0772</v>
+        <v>-2.0988</v>
       </c>
       <c r="R8" t="n">
-        <v>6.230399999999999</v>
+        <v>6.295199999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9771</v>
+        <v>4.0323</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2984</v>
+        <v>1.1625</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6784</v>
+        <v>2.8698</v>
       </c>
       <c r="V8" t="n">
-        <v>2.7924</v>
+        <v>2.7903</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6155</v>
+        <v>1.6011</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1769</v>
+        <v>1.1892</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.035</v>
+        <v>4.0716</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0249</v>
+        <v>0.0156</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0101</v>
+        <v>4.0557</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2287</v>
+        <v>2.235</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1082</v>
+        <v>1.1148</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1205</v>
+        <v>1.1202</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2124</v>
+        <v>0.21</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1014</v>
+        <v>0.1002</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1107</v>
+        <v>0.1101</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0163</v>
+        <v>2.025</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0065</v>
+        <v>1.0149</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0095</v>
+        <v>1.0101</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3845</v>
+        <v>1.3989</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4218</v>
+        <v>0.4374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1875</v>
+        <v>-0.1944</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6093</v>
+        <v>0.6318</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>3.632400000000001</v>
+        <v>3.9024</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2012</v>
+        <v>15.7533</v>
       </c>
       <c r="F10" t="n">
-        <v>-12.5691</v>
+        <v>-11.8509</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7925999999999997</v>
+        <v>-0.6936</v>
       </c>
       <c r="H10" t="n">
-        <v>6.466500000000001</v>
+        <v>6.4566</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.2591</v>
+        <v>-7.1508</v>
       </c>
       <c r="J10" t="n">
-        <v>9.827999999999999</v>
+        <v>9.6564</v>
       </c>
       <c r="K10" t="n">
-        <v>9.0525</v>
+        <v>8.886000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7752</v>
+        <v>0.7704</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.6203</v>
+        <v>-10.35</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5854</v>
+        <v>-2.4294</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.034599999999999</v>
+        <v>-7.9206</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.000299999999999967</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8459</v>
+        <v>-4.8966</v>
       </c>
       <c r="R10" t="n">
-        <v>4.8459</v>
+        <v>4.8963</v>
       </c>
       <c r="S10" t="n">
-        <v>8.0943</v>
+        <v>8.2104</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8802</v>
+        <v>3.7659</v>
       </c>
       <c r="U10" t="n">
-        <v>4.2141</v>
+        <v>4.4439</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6696</v>
+        <v>-3.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>7.3392</v>
+        <v>7.2276</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.0088</v>
+        <v>-10.8414</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9029</v>
+        <v>-1.7568</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5030999999999999</v>
+        <v>-1.4178</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4001</v>
+        <v>-0.3389999999999995</v>
       </c>
       <c r="G11" t="n">
-        <v>-16.7085</v>
+        <v>-16.7064</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7454</v>
+        <v>4.617900000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-21.4539</v>
+        <v>-21.324</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0421</v>
+        <v>-2.4774</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8714</v>
+        <v>7.4967</v>
       </c>
       <c r="L11" t="n">
-        <v>-9.913799999999998</v>
+        <v>-9.9747</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.6658</v>
+        <v>-14.2287</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.126</v>
+        <v>-2.8791</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.5401</v>
+        <v>-11.3499</v>
       </c>
       <c r="P11" t="n">
-        <v>5.5383</v>
+        <v>5.596200000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.6149</v>
+        <v>-7.6944</v>
       </c>
       <c r="R11" t="n">
-        <v>13.1532</v>
+        <v>13.2906</v>
       </c>
       <c r="S11" t="n">
-        <v>6.7746</v>
+        <v>6.9291</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1994999999999999</v>
+        <v>-0.07410000000000008</v>
       </c>
       <c r="U11" t="n">
-        <v>6.5751</v>
+        <v>7.0032</v>
       </c>
       <c r="V11" t="n">
-        <v>2.492700000000001</v>
+        <v>2.424599999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>8.954700000000001</v>
+        <v>8.8287</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.462</v>
+        <v>-6.4041</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.395</v>
+        <v>-7.267499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2619</v>
+        <v>-4.178700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.1328</v>
+        <v>-3.0888</v>
       </c>
       <c r="G12" t="n">
-        <v>-25.9071</v>
+        <v>-25.7742</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.7956</v>
+        <v>-6.8484</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.1118</v>
+        <v>-18.9261</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.247</v>
+        <v>-2.6301</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8943000000000002</v>
+        <v>0.5442</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.141</v>
+        <v>-3.174300000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.6604</v>
+        <v>-23.1441</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.6896</v>
+        <v>-7.3926</v>
       </c>
       <c r="O12" t="n">
-        <v>-15.9711</v>
+        <v>-15.7515</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4611</v>
+        <v>3.4974</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.7684</v>
+        <v>-11.8917</v>
       </c>
       <c r="R12" t="n">
-        <v>15.2298</v>
+        <v>15.3888</v>
       </c>
       <c r="S12" t="n">
-        <v>7.7121</v>
+        <v>7.781700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.976</v>
+        <v>2.7036</v>
       </c>
       <c r="U12" t="n">
-        <v>4.7367</v>
+        <v>5.0781</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3392</v>
+        <v>7.2279</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7778</v>
+        <v>7.6398</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4386</v>
+        <v>-0.4119</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-38.2467</v>
+        <v>-38.3448</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.3639</v>
+        <v>-22.4781</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.8828</v>
+        <v>-15.8667</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.0943</v>
+        <v>-11.1342</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3473</v>
+        <v>7.2801</v>
       </c>
       <c r="I13" t="n">
-        <v>-18.4419</v>
+        <v>-18.4146</v>
       </c>
       <c r="J13" t="n">
-        <v>8.311200000000001</v>
+        <v>7.821000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>11.4828</v>
+        <v>11.1696</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.1719</v>
+        <v>-3.348599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.4052</v>
+        <v>-18.9552</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.1355</v>
+        <v>-3.8895</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.27</v>
+        <v>-15.0657</v>
       </c>
       <c r="P13" t="n">
-        <v>-17.9988</v>
+        <v>-18.1872</v>
       </c>
       <c r="Q13" t="n">
-        <v>-30.4596</v>
+        <v>-30.7782</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4608</v>
+        <v>12.5907</v>
       </c>
       <c r="S13" t="n">
-        <v>4.947</v>
+        <v>4.9737</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5228</v>
+        <v>1.2567</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4242</v>
+        <v>3.7173</v>
       </c>
       <c r="V13" t="n">
-        <v>-14.1006</v>
+        <v>-13.9971</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7383000000000001</v>
+        <v>-0.7773</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.3626</v>
+        <v>-13.2198</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>85.09980000000002</v>
+        <v>85.4811</v>
       </c>
       <c r="E14" t="n">
-        <v>139.7937</v>
+        <v>131.6268</v>
       </c>
       <c r="F14" t="n">
-        <v>-54.6939</v>
+        <v>-46.1463</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.48350000000001</v>
+        <v>-19.79910000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>73.62150000000001</v>
+        <v>72.57180000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-93.10650000000001</v>
+        <v>-92.37180000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>109.545</v>
+        <v>105.5055</v>
       </c>
       <c r="K14" t="n">
-        <v>104.7774</v>
+        <v>101.523</v>
       </c>
       <c r="L14" t="n">
-        <v>4.765500000000001</v>
+        <v>3.982199999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-129.0282</v>
+        <v>-125.3043</v>
       </c>
       <c r="N14" t="n">
-        <v>-31.1559</v>
+        <v>-28.9515</v>
       </c>
       <c r="O14" t="n">
-        <v>-97.87259999999999</v>
+        <v>-96.35309999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>17.3079</v>
+        <v>17.4879</v>
       </c>
       <c r="Q14" t="n">
-        <v>-83.0724</v>
+        <v>-83.9406</v>
       </c>
       <c r="R14" t="n">
-        <v>100.3791</v>
+        <v>101.4267</v>
       </c>
       <c r="S14" t="n">
-        <v>57.18300000000001</v>
+        <v>58.1058</v>
       </c>
       <c r="T14" t="n">
-        <v>13.7823</v>
+        <v>11.8047</v>
       </c>
       <c r="U14" t="n">
-        <v>43.401</v>
+        <v>46.3008</v>
       </c>
       <c r="V14" t="n">
-        <v>30.0954</v>
+        <v>29.6886</v>
       </c>
       <c r="W14" t="n">
-        <v>99.53909999999999</v>
+        <v>98.259</v>
       </c>
       <c r="X14" t="n">
-        <v>-69.4443</v>
+        <v>-68.57040000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>34.6902</v>
+        <v>12.1704</v>
       </c>
       <c r="E2" t="n">
-        <v>34.7346</v>
+        <v>15.4698</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04469999999999974</v>
+        <v>-3.2994</v>
       </c>
       <c r="G2" t="n">
-        <v>11.0841</v>
+        <v>8.538600000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>10.074</v>
+        <v>6.248200000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0101</v>
+        <v>2.2904</v>
       </c>
       <c r="J2" t="n">
-        <v>18.9759</v>
+        <v>11.5766</v>
       </c>
       <c r="K2" t="n">
-        <v>11.4696</v>
+        <v>6.9624</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5063</v>
+        <v>4.6142</v>
       </c>
       <c r="M2" t="n">
-        <v>-7.8921</v>
+        <v>-3.038</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3962</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.4962</v>
+        <v>-2.3238</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0985</v>
+        <v>1.1475</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.9948</v>
+        <v>-1.1475</v>
       </c>
       <c r="R2" t="n">
-        <v>9.0936</v>
+        <v>2.295</v>
       </c>
       <c r="S2" t="n">
-        <v>4.674</v>
+        <v>1.1004</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7056</v>
+        <v>0.4108</v>
       </c>
       <c r="U2" t="n">
-        <v>3.9687</v>
+        <v>0.6898</v>
       </c>
       <c r="V2" t="n">
-        <v>16.8336</v>
+        <v>1.3838</v>
       </c>
       <c r="W2" t="n">
-        <v>22.0485</v>
+        <v>4.6298</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.2149</v>
+        <v>-3.246</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>27.1182</v>
+        <v>8.933299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>32.0802</v>
+        <v>10.3631</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.9617</v>
+        <v>-1.4299</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.8452</v>
+        <v>-1.997400000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9728999999999999</v>
+        <v>4.1966</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.8181</v>
+        <v>-6.194099999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>10.3641</v>
+        <v>5.2903</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3949</v>
+        <v>4.4788</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9695</v>
+        <v>0.8114999999999997</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.209</v>
+        <v>-7.2875</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.4217</v>
+        <v>-0.2822</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.787599999999999</v>
+        <v>-7.0055</v>
       </c>
       <c r="P3" t="n">
-        <v>11.1921</v>
+        <v>1.6065</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.213</v>
       </c>
       <c r="R3" t="n">
-        <v>11.1921</v>
+        <v>4.819500000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>4.362299999999999</v>
+        <v>3.7631</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4911</v>
+        <v>1.643</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8712</v>
+        <v>2.1201</v>
       </c>
       <c r="V3" t="n">
-        <v>14.409</v>
+        <v>5.5609</v>
       </c>
       <c r="W3" t="n">
-        <v>21.225</v>
+        <v>6.6431</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.816</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>23.8812</v>
+        <v>7.983700000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>29.2488</v>
+        <v>10.1261</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.367599999999999</v>
+        <v>-2.1425</v>
       </c>
       <c r="G4" t="n">
-        <v>5.693700000000001</v>
+        <v>-1.5605</v>
       </c>
       <c r="H4" t="n">
-        <v>22.791</v>
+        <v>2.3429</v>
       </c>
       <c r="I4" t="n">
-        <v>-17.0973</v>
+        <v>-3.9034</v>
       </c>
       <c r="J4" t="n">
-        <v>28.9242</v>
+        <v>4.062200000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>28.6635</v>
+        <v>4.0185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2601</v>
+        <v>0.0437</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.2302</v>
+        <v>-5.6227</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.8728</v>
+        <v>-1.6756</v>
       </c>
       <c r="O4" t="n">
-        <v>-17.3574</v>
+        <v>-3.9471</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6996</v>
+        <v>3.4425</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13.2906</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>13.9899</v>
+        <v>3.4425</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8692</v>
+        <v>0.9311</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01619999999999988</v>
+        <v>0.3521</v>
       </c>
       <c r="U4" t="n">
-        <v>5.8854</v>
+        <v>0.5790000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>11.6187</v>
+        <v>5.1708</v>
       </c>
       <c r="W4" t="n">
-        <v>13.6317</v>
+        <v>5.7118</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.013</v>
+        <v>-0.541</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>11.4582</v>
+        <v>6.2253</v>
       </c>
       <c r="E5" t="n">
-        <v>19.4517</v>
+        <v>5.5774</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.9938</v>
+        <v>0.6477999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>5.234999999999999</v>
+        <v>5.1443</v>
       </c>
       <c r="H5" t="n">
-        <v>8.3361</v>
+        <v>3.2615</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1011</v>
+        <v>1.8829</v>
       </c>
       <c r="J5" t="n">
-        <v>8.571899999999999</v>
+        <v>6.065099999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>9.759599999999999</v>
+        <v>3.2055</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1877</v>
+        <v>2.8596</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.3369</v>
+        <v>-0.9208</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4235</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9134</v>
+        <v>-0.9766</v>
       </c>
       <c r="P5" t="n">
-        <v>4.896599999999999</v>
+        <v>0.459</v>
       </c>
       <c r="Q5" t="n">
+        <v>-0.459</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.6506</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>4.896599999999999</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5285</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.8616</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.6666</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-3.2019</v>
-      </c>
       <c r="W5" t="n">
-        <v>10.0179</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.2198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10.7358</v>
+        <v>6.099900000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6926</v>
+        <v>7.841399999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9571</v>
+        <v>-1.7415</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3609</v>
+        <v>4.4125</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3143</v>
+        <v>3.4389</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.9534</v>
+        <v>0.9736</v>
       </c>
       <c r="J6" t="n">
-        <v>10.212</v>
+        <v>6.4272</v>
       </c>
       <c r="K6" t="n">
-        <v>9.221400000000001</v>
+        <v>4.4501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9906</v>
+        <v>1.977</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8511</v>
+        <v>-2.0147</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0929</v>
+        <v>-1.0112</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.9437</v>
+        <v>-1.0035</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6996</v>
+        <v>0.6885</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.896599999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>5.5959</v>
+        <v>0.6885</v>
       </c>
       <c r="S6" t="n">
-        <v>5.2764</v>
+        <v>0.9989</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5615</v>
+        <v>0.1812</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7152</v>
+        <v>0.8176</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6008</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>6.816</v>
+        <v>1.2329</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.4168</v>
+        <v>-1.2329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10.3077</v>
+        <v>5.5381</v>
       </c>
       <c r="E7" t="n">
-        <v>12.2652</v>
+        <v>4.785600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9575</v>
+        <v>0.7525000000000002</v>
       </c>
       <c r="G7" t="n">
-        <v>11.0805</v>
+        <v>1.3016</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1338</v>
+        <v>3.703</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9467</v>
+        <v>-2.4014</v>
       </c>
       <c r="J7" t="n">
-        <v>14.0832</v>
+        <v>3.4312</v>
       </c>
       <c r="K7" t="n">
-        <v>7.5846</v>
+        <v>3.2325</v>
       </c>
       <c r="L7" t="n">
-        <v>6.4986</v>
+        <v>0.1986999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0033</v>
+        <v>-2.1296</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4511</v>
+        <v>0.4705</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5519</v>
+        <v>-2.6001</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3992</v>
+        <v>0.6885</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3989</v>
+        <v>-0.6885</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7981</v>
+        <v>1.377</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0308</v>
+        <v>2.0758</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4191</v>
+        <v>0.9609000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4496</v>
+        <v>1.1149</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.2019</v>
+        <v>1.4721</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2019</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>6.6849</v>
+        <v>4.0225</v>
       </c>
       <c r="E8" t="n">
-        <v>2.459399999999999</v>
+        <v>5.4063</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2258</v>
+        <v>-1.3838</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3347</v>
+        <v>4.0047</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3287</v>
+        <v>5.6448</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.6634</v>
+        <v>-1.64</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7943</v>
+        <v>5.6518</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2327</v>
+        <v>5.3184</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5619000000000003</v>
+        <v>0.3335</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.1287</v>
+        <v>-1.6471</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09659999999999991</v>
+        <v>0.3264</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.2253</v>
+        <v>-1.9735</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1973</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0988</v>
+        <v>-2.5245</v>
       </c>
       <c r="R8" t="n">
-        <v>6.295199999999999</v>
+        <v>1.377</v>
       </c>
       <c r="S8" t="n">
-        <v>4.0323</v>
+        <v>1.4668</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1625</v>
+        <v>0.1147</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8698</v>
+        <v>1.3521</v>
       </c>
       <c r="V8" t="n">
-        <v>2.7903</v>
+        <v>-0.3018000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6011</v>
+        <v>2.164</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1892</v>
+        <v>-2.4658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>M. SISSOKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4.0716</v>
+        <v>3.7311</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0156</v>
+        <v>5.568</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0557</v>
+        <v>-1.8369</v>
       </c>
       <c r="G9" t="n">
-        <v>2.235</v>
+        <v>2.0334</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1148</v>
+        <v>2.5787</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1202</v>
+        <v>-0.5454</v>
       </c>
       <c r="J9" t="n">
-        <v>0.21</v>
+        <v>3.3924</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1002</v>
+        <v>3.096</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1101</v>
+        <v>0.2964</v>
       </c>
       <c r="M9" t="n">
-        <v>2.025</v>
+        <v>-1.3591</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0149</v>
+        <v>-0.5173</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0101</v>
+        <v>-0.8418</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3989</v>
+        <v>-1.377</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9835</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3989</v>
+        <v>1.6065</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4374</v>
+        <v>4.005800000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1944</v>
+        <v>2.3914</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6318</v>
+        <v>1.6144</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9311</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.7674</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.698700000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SISSOKO</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3.9024</v>
+        <v>1.9574</v>
       </c>
       <c r="E10" t="n">
-        <v>15.7533</v>
+        <v>4.0557</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.8509</v>
+        <v>-2.0985</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6936</v>
+        <v>-8.552999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4566</v>
+        <v>-1.2443</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.1508</v>
+        <v>-7.3087</v>
       </c>
       <c r="J10" t="n">
-        <v>9.6564</v>
+        <v>0.4635</v>
       </c>
       <c r="K10" t="n">
-        <v>8.886000000000001</v>
+        <v>-0.1361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7704</v>
+        <v>0.5996</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.35</v>
+        <v>-9.0162</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4294</v>
+        <v>-1.1082</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.9206</v>
+        <v>-7.9082</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.000299999999999967</v>
+        <v>3.4425</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8966</v>
+        <v>-1.836</v>
       </c>
       <c r="R10" t="n">
-        <v>4.8963</v>
+        <v>5.2785</v>
       </c>
       <c r="S10" t="n">
-        <v>8.2104</v>
+        <v>4.752899999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7659</v>
+        <v>2.9626</v>
       </c>
       <c r="U10" t="n">
-        <v>4.4439</v>
+        <v>1.7903</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6138</v>
+        <v>2.315</v>
       </c>
       <c r="W10" t="n">
-        <v>7.2276</v>
+        <v>2.4658</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.8414</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7568</v>
+        <v>1.3206</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4178</v>
+        <v>0.0033</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3389999999999995</v>
+        <v>1.3173</v>
       </c>
       <c r="G11" t="n">
-        <v>-16.7064</v>
+        <v>0.7091</v>
       </c>
       <c r="H11" t="n">
-        <v>4.617900000000001</v>
+        <v>0.3487</v>
       </c>
       <c r="I11" t="n">
-        <v>-21.324</v>
+        <v>0.3604</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4774</v>
+        <v>0.0712</v>
       </c>
       <c r="K11" t="n">
-        <v>7.4967</v>
+        <v>0.0341</v>
       </c>
       <c r="L11" t="n">
-        <v>-9.9747</v>
+        <v>0.0371</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.2287</v>
+        <v>0.6379</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.8791</v>
+        <v>0.3146</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.3499</v>
+        <v>0.3234</v>
       </c>
       <c r="P11" t="n">
-        <v>5.596200000000001</v>
+        <v>0.459</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.6944</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>13.2906</v>
+        <v>0.459</v>
       </c>
       <c r="S11" t="n">
-        <v>6.9291</v>
+        <v>0.1526</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07410000000000008</v>
+        <v>-0.0678</v>
       </c>
       <c r="U11" t="n">
-        <v>7.0032</v>
+        <v>0.2204</v>
       </c>
       <c r="V11" t="n">
-        <v>2.424599999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>8.8287</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.4041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.267499999999998</v>
+        <v>-0.3324999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.178700000000001</v>
+        <v>2.8656</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0888</v>
+        <v>-3.1981</v>
       </c>
       <c r="G12" t="n">
-        <v>-25.7742</v>
+        <v>-5.6282</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.8484</v>
+        <v>-0.2322000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>-18.9261</v>
+        <v>-5.396</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6301</v>
+        <v>0.8328999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5442</v>
+        <v>0.867</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.174300000000001</v>
+        <v>-0.0340999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.1441</v>
+        <v>-6.4611</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.3926</v>
+        <v>-1.0994</v>
       </c>
       <c r="O12" t="n">
-        <v>-15.7515</v>
+        <v>-5.3617</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4974</v>
+        <v>2.754</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.8917</v>
+        <v>-1.1475</v>
       </c>
       <c r="R12" t="n">
-        <v>15.3888</v>
+        <v>3.9015</v>
       </c>
       <c r="S12" t="n">
-        <v>7.781700000000001</v>
+        <v>1.6991</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7036</v>
+        <v>0.1734</v>
       </c>
       <c r="U12" t="n">
-        <v>5.0781</v>
+        <v>1.5255</v>
       </c>
       <c r="V12" t="n">
-        <v>7.2279</v>
+        <v>0.8428000000000002</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6398</v>
+        <v>3.0068</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4119</v>
+        <v>-2.164</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-38.3448</v>
+        <v>-21.8277</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.4781</v>
+        <v>-17.2659</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.8667</v>
+        <v>-4.561800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.1342</v>
+        <v>-13.1497</v>
       </c>
       <c r="H13" t="n">
-        <v>7.2801</v>
+        <v>1.3446</v>
       </c>
       <c r="I13" t="n">
-        <v>-18.4146</v>
+        <v>-14.4943</v>
       </c>
       <c r="J13" t="n">
-        <v>7.821000000000001</v>
+        <v>-6.3063</v>
       </c>
       <c r="K13" t="n">
-        <v>11.1696</v>
+        <v>1.762</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.348599999999999</v>
+        <v>-8.068299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-18.9552</v>
+        <v>-6.843500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.8895</v>
+        <v>-0.4172</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.0657</v>
+        <v>-6.426</v>
       </c>
       <c r="P13" t="n">
-        <v>-18.1872</v>
+        <v>-7.573299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-30.7782</v>
+        <v>-12.3928</v>
       </c>
       <c r="R13" t="n">
-        <v>12.5907</v>
+        <v>4.8195</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9737</v>
+        <v>3.7019</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2567</v>
+        <v>1.9116</v>
       </c>
       <c r="U13" t="n">
-        <v>3.7173</v>
+        <v>1.7904</v>
       </c>
       <c r="V13" t="n">
-        <v>-13.9971</v>
+        <v>-4.8066</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7773</v>
+        <v>-0.4786</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.2198</v>
+        <v>-4.328</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>85.4811</v>
+        <v>35.8221</v>
       </c>
       <c r="E14" t="n">
-        <v>131.6268</v>
+        <v>54.79639999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-46.1463</v>
+        <v>-18.9748</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.79910000000001</v>
+        <v>-4.7446</v>
       </c>
       <c r="H14" t="n">
-        <v>72.57180000000001</v>
+        <v>31.6314</v>
       </c>
       <c r="I14" t="n">
-        <v>-92.37180000000001</v>
+        <v>-36.376</v>
       </c>
       <c r="J14" t="n">
-        <v>105.5055</v>
+        <v>40.9581</v>
       </c>
       <c r="K14" t="n">
-        <v>101.523</v>
+        <v>37.2892</v>
       </c>
       <c r="L14" t="n">
-        <v>3.982199999999997</v>
+        <v>3.668900000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-125.3043</v>
+        <v>-45.7024</v>
       </c>
       <c r="N14" t="n">
-        <v>-28.9515</v>
+        <v>-5.6578</v>
       </c>
       <c r="O14" t="n">
-        <v>-96.35309999999998</v>
+        <v>-40.0444</v>
       </c>
       <c r="P14" t="n">
-        <v>17.4879</v>
+        <v>4.5902</v>
       </c>
       <c r="Q14" t="n">
-        <v>-83.9406</v>
+        <v>-26.3923</v>
       </c>
       <c r="R14" t="n">
-        <v>101.4267</v>
+        <v>30.9825</v>
       </c>
       <c r="S14" t="n">
-        <v>58.1058</v>
+        <v>25.2704</v>
       </c>
       <c r="T14" t="n">
-        <v>11.8047</v>
+        <v>11.0052</v>
       </c>
       <c r="U14" t="n">
-        <v>46.3008</v>
+        <v>14.2651</v>
       </c>
       <c r="V14" t="n">
-        <v>29.6886</v>
+        <v>10.7059</v>
       </c>
       <c r="W14" t="n">
-        <v>98.259</v>
+        <v>29.225</v>
       </c>
       <c r="X14" t="n">
-        <v>-68.57040000000001</v>
+        <v>-18.5192</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1704</v>
+        <v>12.0324</v>
       </c>
       <c r="E2" t="n">
-        <v>15.4698</v>
+        <v>14.9196</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2994</v>
+        <v>-2.8873</v>
       </c>
       <c r="G2" t="n">
-        <v>8.538600000000001</v>
+        <v>8.3681</v>
       </c>
       <c r="H2" t="n">
-        <v>6.248200000000001</v>
+        <v>6.0964</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2904</v>
+        <v>2.2718</v>
       </c>
       <c r="J2" t="n">
-        <v>11.5766</v>
+        <v>11.2291</v>
       </c>
       <c r="K2" t="n">
-        <v>6.9624</v>
+        <v>6.6978</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6142</v>
+        <v>4.5314</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.038</v>
+        <v>-2.861</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6013999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.3238</v>
+        <v>-2.2596</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1475</v>
+        <v>1.1698</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R2" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1004</v>
+        <v>1.1616</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4108</v>
+        <v>0.3352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6898</v>
+        <v>0.8264</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3838</v>
+        <v>1.3327</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6298</v>
+        <v>4.5251</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.246</v>
+        <v>-3.1924</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8.933299999999999</v>
+        <v>8.9109</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3631</v>
+        <v>9.6839</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4299</v>
+        <v>-0.7732</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.997400000000001</v>
+        <v>-2.056400000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1966</v>
+        <v>4.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.194099999999999</v>
+        <v>-6.110300000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2903</v>
+        <v>4.953899999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4788</v>
+        <v>4.1975</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8114999999999997</v>
+        <v>0.7565</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.2875</v>
+        <v>-7.010400000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2822</v>
+        <v>-0.1435999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.0055</v>
+        <v>-6.8668</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.213</v>
+        <v>-3.2755</v>
       </c>
       <c r="R3" t="n">
-        <v>4.819500000000001</v>
+        <v>4.9133</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7631</v>
+        <v>3.8746</v>
       </c>
       <c r="T3" t="n">
-        <v>1.643</v>
+        <v>1.4865</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1201</v>
+        <v>2.3879</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5609</v>
+        <v>5.454899999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>6.6431</v>
+        <v>6.518899999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.082</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.983700000000001</v>
+        <v>7.8756</v>
       </c>
       <c r="E4" t="n">
-        <v>10.1261</v>
+        <v>9.5976</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1425</v>
+        <v>-1.722</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5605</v>
+        <v>-1.6353</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3429</v>
+        <v>2.1831</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.9034</v>
+        <v>-3.8184</v>
       </c>
       <c r="J4" t="n">
-        <v>4.062200000000001</v>
+        <v>3.7834</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0185</v>
+        <v>3.7492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0437</v>
+        <v>0.03420000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.6227</v>
+        <v>-5.418699999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6756</v>
+        <v>-1.5661</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.9471</v>
+        <v>-3.8526</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4425</v>
+        <v>3.5095</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4425</v>
+        <v>3.5095</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9311</v>
+        <v>0.9442</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3521</v>
+        <v>0.225</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5790000000000001</v>
+        <v>0.7192</v>
       </c>
       <c r="V4" t="n">
-        <v>5.1708</v>
+        <v>5.0572</v>
       </c>
       <c r="W4" t="n">
-        <v>5.7118</v>
+        <v>5.5892</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2253</v>
+        <v>6.2473</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5774</v>
+        <v>5.4219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6477999999999999</v>
+        <v>0.8255</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1443</v>
+        <v>5.0981</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2615</v>
+        <v>3.2289</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8829</v>
+        <v>1.8692</v>
       </c>
       <c r="J5" t="n">
-        <v>6.065099999999999</v>
+        <v>5.9374</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2055</v>
+        <v>3.1213</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8596</v>
+        <v>2.8159</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9208</v>
+        <v>-0.839</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9766</v>
+        <v>-0.9469</v>
       </c>
       <c r="P5" t="n">
-        <v>0.459</v>
+        <v>0.468</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="R5" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S5" t="n">
-        <v>0.622</v>
+        <v>0.6812</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0287</v>
+        <v>-0.04740000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6506</v>
+        <v>0.7286</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6.099900000000001</v>
+        <v>6.1554</v>
       </c>
       <c r="E6" t="n">
-        <v>7.841399999999999</v>
+        <v>7.568199999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7415</v>
+        <v>-1.4128</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4125</v>
+        <v>4.4005</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4389</v>
+        <v>3.4223</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9736</v>
+        <v>0.9778999999999998</v>
       </c>
       <c r="J6" t="n">
-        <v>6.4272</v>
+        <v>6.2685</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4501</v>
+        <v>4.3332</v>
       </c>
       <c r="L6" t="n">
-        <v>1.977</v>
+        <v>1.935</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0147</v>
+        <v>-1.868</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0112</v>
+        <v>-0.9109</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0035</v>
+        <v>-0.9571000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6885</v>
+        <v>0.7020000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6885</v>
+        <v>0.7020000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9989</v>
+        <v>1.0529</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1812</v>
+        <v>0.1013</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8176</v>
+        <v>0.9516</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5381</v>
+        <v>5.605499999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>4.785600000000001</v>
+        <v>4.5292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7525000000000002</v>
+        <v>1.0763</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3016</v>
+        <v>1.322</v>
       </c>
       <c r="H7" t="n">
-        <v>3.703</v>
+        <v>3.6835</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4014</v>
+        <v>-2.3617</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4312</v>
+        <v>3.3053</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2325</v>
+        <v>3.1271</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1986999999999999</v>
+        <v>0.1781000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1296</v>
+        <v>-1.9835</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4705</v>
+        <v>0.5563</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6001</v>
+        <v>-2.5398</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6885</v>
+        <v>0.7020000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6885</v>
+        <v>-0.7020000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>1.377</v>
+        <v>1.4037</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0758</v>
+        <v>2.1198</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9609000000000001</v>
+        <v>0.8617000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1149</v>
+        <v>1.2581</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4721</v>
+        <v>1.462</v>
       </c>
       <c r="W7" t="n">
-        <v>1.082</v>
+        <v>1.0642</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.0225</v>
+        <v>4.0008</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4063</v>
+        <v>5.0046</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3838</v>
+        <v>-1.0038</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0047</v>
+        <v>3.8834</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6448</v>
+        <v>5.4803</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.64</v>
+        <v>-1.597</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6518</v>
+        <v>5.4058</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3184</v>
+        <v>5.0764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3335</v>
+        <v>0.3294</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6471</v>
+        <v>-1.5224</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3264</v>
+        <v>0.4036999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9735</v>
+        <v>-1.9264</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1475</v>
+        <v>-1.1698</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5245</v>
+        <v>-2.5738</v>
       </c>
       <c r="R8" t="n">
-        <v>1.377</v>
+        <v>1.4037</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4668</v>
+        <v>1.5558</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1147</v>
+        <v>0.04430000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3521</v>
+        <v>1.5116</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3018000000000001</v>
+        <v>-0.2685999999999997</v>
       </c>
       <c r="W8" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4658</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7311</v>
+        <v>3.8532</v>
       </c>
       <c r="E9" t="n">
-        <v>5.568</v>
+        <v>5.2252</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8369</v>
+        <v>-1.372</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0334</v>
+        <v>2.0697</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5787</v>
+        <v>2.5724</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5454</v>
+        <v>-0.5026999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3924</v>
+        <v>3.2872</v>
       </c>
       <c r="K9" t="n">
-        <v>3.096</v>
+        <v>2.9943</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2964</v>
+        <v>0.2928</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3591</v>
+        <v>-1.2174</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5173</v>
+        <v>-0.4219</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8418</v>
+        <v>-0.7955000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.377</v>
+        <v>-1.4039</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9835</v>
+        <v>-3.0416</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6065</v>
+        <v>1.6377</v>
       </c>
       <c r="S9" t="n">
-        <v>4.005800000000001</v>
+        <v>4.117</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3914</v>
+        <v>2.3141</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6144</v>
+        <v>1.8027</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9311</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7674</v>
+        <v>2.6655</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.698700000000001</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9574</v>
+        <v>2.0766</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0557</v>
+        <v>3.5257</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0985</v>
+        <v>-1.4492</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.552999999999999</v>
+        <v>-8.515600000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2443</v>
+        <v>-1.3384</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.3087</v>
+        <v>-7.1771</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4635</v>
+        <v>0.2051</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1361</v>
+        <v>-0.3781</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5996</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-9.0162</v>
+        <v>-8.720600000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1082</v>
+        <v>-0.9602999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.9082</v>
+        <v>-7.7603</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4425</v>
+        <v>3.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="R10" t="n">
-        <v>5.2785</v>
+        <v>5.3813</v>
       </c>
       <c r="S10" t="n">
-        <v>4.752899999999999</v>
+        <v>4.82</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9626</v>
+        <v>2.7957</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7903</v>
+        <v>2.0243</v>
       </c>
       <c r="V10" t="n">
-        <v>2.315</v>
+        <v>2.2625</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4658</v>
+        <v>2.3968</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3206</v>
+        <v>1.3424</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0033</v>
+        <v>-0.0026</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3173</v>
+        <v>1.345</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7091</v>
+        <v>0.7115</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3487</v>
+        <v>0.3518</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3604</v>
+        <v>0.3597</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0712</v>
+        <v>0.0698</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0341</v>
+        <v>0.0332</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6379</v>
+        <v>0.6417</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3146</v>
+        <v>0.3186</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3234</v>
+        <v>0.3231</v>
       </c>
       <c r="P11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1526</v>
+        <v>0.163</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0678</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2204</v>
+        <v>0.2354</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3324999999999999</v>
+        <v>-0.2525999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8656</v>
+        <v>2.3199</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1981</v>
+        <v>-2.5725</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6282</v>
+        <v>-5.6452</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2322000000000002</v>
+        <v>-0.3164000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.396</v>
+        <v>-5.3288</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8328999999999999</v>
+        <v>0.5518000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.867</v>
+        <v>0.6395999999999997</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0340999999999998</v>
+        <v>-0.0878000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.4611</v>
+        <v>-6.197</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0994</v>
+        <v>-0.9557</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.3617</v>
+        <v>-5.241</v>
       </c>
       <c r="P12" t="n">
-        <v>2.754</v>
+        <v>2.8077</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9015</v>
+        <v>3.9775</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6991</v>
+        <v>1.7843</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1734</v>
+        <v>0.009099999999999997</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5255</v>
+        <v>1.7752</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8428000000000002</v>
+        <v>0.8005999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>3.0068</v>
+        <v>2.9289</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.8277</v>
+        <v>-21.8215</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.2659</v>
+        <v>-17.9149</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.561800000000001</v>
+        <v>-3.9067</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.1497</v>
+        <v>-13.087</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3446</v>
+        <v>1.3422</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.4943</v>
+        <v>-14.4292</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.3063</v>
+        <v>-6.499200000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.762</v>
+        <v>1.6338</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.068299999999999</v>
+        <v>-8.132999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.843500000000001</v>
+        <v>-6.5878</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4172</v>
+        <v>-0.2918000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.426</v>
+        <v>-6.2962</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.573299999999999</v>
+        <v>-7.7211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.3928</v>
+        <v>-12.6345</v>
       </c>
       <c r="R13" t="n">
-        <v>4.8195</v>
+        <v>4.9135</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7019</v>
+        <v>3.77</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9116</v>
+        <v>1.7457</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7904</v>
+        <v>2.0243</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.8066</v>
+        <v>-4.7834</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4786</v>
+        <v>-0.5268</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.328</v>
+        <v>-4.2564</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>35.8221</v>
+        <v>36.026</v>
       </c>
       <c r="E14" t="n">
-        <v>54.79639999999999</v>
+        <v>49.8783</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.9748</v>
+        <v>-13.8527</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.7446</v>
+        <v>-5.086200000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>31.6314</v>
+        <v>30.76</v>
       </c>
       <c r="I14" t="n">
-        <v>-36.376</v>
+        <v>-35.8466</v>
       </c>
       <c r="J14" t="n">
-        <v>40.9581</v>
+        <v>38.49809999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>37.2892</v>
+        <v>35.2253</v>
       </c>
       <c r="L14" t="n">
-        <v>3.668900000000002</v>
+        <v>3.272300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-45.7024</v>
+        <v>-43.58410000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6578</v>
+        <v>-4.4655</v>
       </c>
       <c r="O14" t="n">
-        <v>-40.0444</v>
+        <v>-39.1191</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5902</v>
+        <v>4.679500000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-26.3923</v>
+        <v>-26.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>30.9825</v>
+        <v>31.5857</v>
       </c>
       <c r="S14" t="n">
-        <v>25.2704</v>
+        <v>26.0444</v>
       </c>
       <c r="T14" t="n">
-        <v>11.0052</v>
+        <v>9.798799999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>14.2651</v>
+        <v>16.2453</v>
       </c>
       <c r="V14" t="n">
-        <v>10.7059</v>
+        <v>10.388</v>
       </c>
       <c r="W14" t="n">
-        <v>29.225</v>
+        <v>28.4884</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.5192</v>
+        <v>-18.1002</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,73 +565,73 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0324</v>
+        <v>11.6137</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9196</v>
+        <v>11.7542</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8873</v>
+        <v>-0.1405000000000002</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3681</v>
+        <v>3.6879</v>
       </c>
       <c r="H2" t="n">
-        <v>6.0964</v>
+        <v>3.3614</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2718</v>
+        <v>0.3266</v>
       </c>
       <c r="J2" t="n">
-        <v>11.2291</v>
+        <v>6.593599999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6978</v>
+        <v>3.9722</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5314</v>
+        <v>2.6214</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.861</v>
+        <v>-2.9056</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6013999999999999</v>
+        <v>-0.6108</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2596</v>
+        <v>-2.2949</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1698</v>
+        <v>0.6962</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1699</v>
+        <v>-2.3208</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3397</v>
+        <v>3.0169</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1616</v>
+        <v>1.5882</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3352</v>
+        <v>0.0912</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8264</v>
+        <v>1.4971</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3327</v>
+        <v>5.6412</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5251</v>
+        <v>7.3901</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.1924</v>
+        <v>-1.7489</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8.9109</v>
+        <v>9.095600000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>9.6839</v>
+        <v>10.8717</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7732</v>
+        <v>-1.7761</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.056400000000001</v>
+        <v>-0.895</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0539</v>
+        <v>0.4318</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.110300000000001</v>
+        <v>-1.3268</v>
       </c>
       <c r="J3" t="n">
-        <v>4.953899999999999</v>
+        <v>3.7722</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1975</v>
+        <v>2.027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7565</v>
+        <v>1.7453</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.010400000000001</v>
+        <v>-4.6672</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1435999999999999</v>
+        <v>-1.5952</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.8668</v>
+        <v>-3.072</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6378</v>
+        <v>3.7131</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2755</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4.9133</v>
+        <v>3.7131</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8746</v>
+        <v>1.4547</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4865</v>
+        <v>-0.007900000000000035</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3879</v>
+        <v>1.4627</v>
       </c>
       <c r="V3" t="n">
-        <v>5.454899999999999</v>
+        <v>4.822699999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>6.518899999999999</v>
+        <v>7.1074</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0642</v>
+        <v>-2.2848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.8756</v>
+        <v>8.040800000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9.5976</v>
+        <v>9.966000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.722</v>
+        <v>-1.9252</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6353</v>
+        <v>1.9285</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1831</v>
+        <v>7.6221</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.8184</v>
+        <v>-5.6937</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7834</v>
+        <v>10.0549</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7492</v>
+        <v>9.772300000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03420000000000001</v>
+        <v>0.2826999999999997</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.418699999999999</v>
+        <v>-8.1265</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5661</v>
+        <v>-2.1501</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.8526</v>
+        <v>-5.9763</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5095</v>
+        <v>0.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.4093</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5095</v>
+        <v>4.6414</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9442</v>
+        <v>1.988</v>
       </c>
       <c r="T4" t="n">
-        <v>0.225</v>
+        <v>-0.2492</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7192</v>
+        <v>2.2371</v>
       </c>
       <c r="V4" t="n">
-        <v>5.0572</v>
+        <v>3.8923</v>
       </c>
       <c r="W4" t="n">
-        <v>5.5892</v>
+        <v>4.5694</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5321</v>
+        <v>-0.6772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2473</v>
+        <v>3.7555</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4219</v>
+        <v>6.523300000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8255</v>
+        <v>-2.7678</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0981</v>
+        <v>1.6661</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2289</v>
+        <v>2.6917</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8692</v>
+        <v>-1.0256</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9374</v>
+        <v>2.9893</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1213</v>
+        <v>3.2746</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8159</v>
+        <v>-0.2852000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.839</v>
+        <v>-1.3233</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1076</v>
+        <v>-0.5829</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9469</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.468</v>
+        <v>1.6246</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4679</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9359</v>
+        <v>1.6246</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6812</v>
+        <v>1.5367</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.04740000000000001</v>
+        <v>0.1775</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7286</v>
+        <v>1.3593</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.0717</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.3564</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-4.428100000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6.1554</v>
+        <v>3.616</v>
       </c>
       <c r="E6" t="n">
-        <v>7.568199999999999</v>
+        <v>4.680800000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4128</v>
+        <v>-1.0649</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4005</v>
+        <v>2.1338</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4223</v>
+        <v>3.5227</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9778999999999998</v>
+        <v>-1.3889</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2685</v>
+        <v>3.611</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3332</v>
+        <v>3.2799</v>
       </c>
       <c r="L6" t="n">
-        <v>1.935</v>
+        <v>0.3312</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.868</v>
+        <v>-1.4772</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9109</v>
+        <v>0.2428</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9571000000000001</v>
+        <v>-1.72</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7020000000000001</v>
+        <v>0.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.6246</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7020000000000001</v>
+        <v>1.8565</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0529</v>
+        <v>1.7859</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1013</v>
+        <v>0.4095</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9516</v>
+        <v>1.3764</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5357999999999998</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1984</v>
+        <v>2.2847</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1984</v>
+        <v>-2.8206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.605499999999999</v>
+        <v>3.4154</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5292</v>
+        <v>4.1293</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0763</v>
+        <v>-0.7139</v>
       </c>
       <c r="G7" t="n">
-        <v>1.322</v>
+        <v>3.6466</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6835</v>
+        <v>2.0208</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3617</v>
+        <v>1.6258</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3053</v>
+        <v>4.776400000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1271</v>
+        <v>2.5758</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1781000000000001</v>
+        <v>2.2007</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9835</v>
+        <v>-1.1298</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5563</v>
+        <v>-0.5551</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.5398</v>
+        <v>-0.5748</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7020000000000001</v>
+        <v>0.4642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.7020000000000001</v>
+        <v>-0.4641</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4037</v>
+        <v>0.9283</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1198</v>
+        <v>0.3764</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8617000000000001</v>
+        <v>-0.183</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2581</v>
+        <v>0.5594</v>
       </c>
       <c r="V7" t="n">
-        <v>1.462</v>
+        <v>-1.0717</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0642</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3978</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.0008</v>
+        <v>2.154</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0046</v>
+        <v>0.8466</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0038</v>
+        <v>1.3075</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8834</v>
+        <v>-1.5183</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4803</v>
+        <v>0.4087000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.597</v>
+        <v>-1.9271</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4058</v>
+        <v>0.7501000000000002</v>
       </c>
       <c r="K8" t="n">
-        <v>5.0764</v>
+        <v>0.5065000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3294</v>
+        <v>0.2435999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5224</v>
+        <v>-2.2684</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4036999999999999</v>
+        <v>-0.0978</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9264</v>
+        <v>-2.1707</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1698</v>
+        <v>1.3925</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5738</v>
+        <v>-0.6963</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4037</v>
+        <v>2.0886</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5558</v>
+        <v>1.3496</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04430000000000001</v>
+        <v>0.2567</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5116</v>
+        <v>1.0928</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2685999999999997</v>
+        <v>0.9304000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1282</v>
+        <v>0.5359</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3968</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SISSOKO</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.8532</v>
+        <v>1.3378</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2252</v>
+        <v>0.0016</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.372</v>
+        <v>1.3362</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0697</v>
+        <v>0.7188</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5724</v>
+        <v>0.3555</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5026999999999999</v>
+        <v>0.3633</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2872</v>
+        <v>0.0704</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9943</v>
+        <v>0.0336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2928</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2174</v>
+        <v>0.6484</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4219</v>
+        <v>0.3219</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7955000000000001</v>
+        <v>0.3265</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4039</v>
+        <v>0.4641</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0416</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6377</v>
+        <v>0.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>4.117</v>
+        <v>0.1548</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3141</v>
+        <v>-0.0688</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8027</v>
+        <v>0.2236</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6655</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>M. SISSOKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0766</v>
+        <v>1.1503</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5257</v>
+        <v>5.1878</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4492</v>
+        <v>-4.0376</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.515600000000001</v>
+        <v>-0.3874</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3384</v>
+        <v>2.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.1771</v>
+        <v>-2.4857</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2051</v>
+        <v>3.27</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3781</v>
+        <v>3.0124</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.2576</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.720600000000001</v>
+        <v>-3.6574</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9602999999999999</v>
+        <v>-0.9141</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.7603</v>
+        <v>-2.7433</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5096</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8718</v>
+        <v>-1.6245</v>
       </c>
       <c r="R10" t="n">
-        <v>5.3813</v>
+        <v>1.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>4.82</v>
+        <v>2.7508</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7957</v>
+        <v>1.1163</v>
       </c>
       <c r="U10" t="n">
-        <v>2.0243</v>
+        <v>1.6344</v>
       </c>
       <c r="V10" t="n">
-        <v>2.2625</v>
+        <v>-1.213</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3968</v>
+        <v>2.4261</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1343</v>
+        <v>-3.639</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3424</v>
+        <v>-0.4677999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0026</v>
+        <v>-0.2596000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.345</v>
+        <v>-0.2079999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7115</v>
+        <v>-5.5136</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3518</v>
+        <v>1.599</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3597</v>
+        <v>-7.1125</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0698</v>
+        <v>-0.4068999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0332</v>
+        <v>2.7322</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0366</v>
+        <v>-3.1391</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6417</v>
+        <v>-5.1066</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3186</v>
+        <v>-1.1333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3231</v>
+        <v>-3.9735</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4679</v>
+        <v>1.8566</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.5528</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4679</v>
+        <v>4.4093</v>
       </c>
       <c r="S11" t="n">
-        <v>0.163</v>
+        <v>2.3708</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.262</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2354</v>
+        <v>2.6327</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.8184000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.9619</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1434</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2525999999999999</v>
+        <v>-2.438</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3199</v>
+        <v>-1.2578</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5725</v>
+        <v>-1.1802</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6452</v>
+        <v>-8.596499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3164000000000002</v>
+        <v>-2.174</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.3288</v>
+        <v>-6.4226</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5518000000000001</v>
+        <v>-0.516</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6395999999999997</v>
+        <v>0.4614</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0878000000000001</v>
+        <v>-0.9774</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.197</v>
+        <v>-8.080500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9557</v>
+        <v>-2.6353</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.241</v>
+        <v>-5.4452</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8077</v>
+        <v>1.1604</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1699</v>
+        <v>-3.9452</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9775</v>
+        <v>5.1056</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7843</v>
+        <v>2.572</v>
       </c>
       <c r="T12" t="n">
-        <v>0.009099999999999997</v>
+        <v>0.6361000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7752</v>
+        <v>1.936</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8005999999999998</v>
+        <v>2.4261</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9289</v>
+        <v>2.567400000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1282</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.8215</v>
+        <v>-12.6861</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.9149</v>
+        <v>-7.2307</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9067</v>
+        <v>-5.4554</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.087</v>
+        <v>-3.599499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3422</v>
+        <v>2.4118</v>
       </c>
       <c r="I13" t="n">
-        <v>-14.4292</v>
+        <v>-6.0112</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.499200000000001</v>
+        <v>3.0594</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6338</v>
+        <v>3.8715</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.132999999999999</v>
+        <v>-0.8121000000000003</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.5878</v>
+        <v>-6.6589</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2918000000000001</v>
+        <v>-1.4598</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.2962</v>
+        <v>-5.1992</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.7211</v>
+        <v>-6.033899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6345</v>
+        <v>-10.2111</v>
       </c>
       <c r="R13" t="n">
-        <v>4.9135</v>
+        <v>4.1774</v>
       </c>
       <c r="S13" t="n">
-        <v>3.77</v>
+        <v>1.6286</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7457</v>
+        <v>0.1741999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0243</v>
+        <v>1.4545</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.7834</v>
+        <v>-4.6814</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5268</v>
+        <v>-0.2532</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.2564</v>
+        <v>-4.4282</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>36.026</v>
+        <v>28.58720000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>49.8783</v>
+        <v>45.2132</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.8527</v>
+        <v>-16.6259</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.086200000000002</v>
+        <v>-6.728599999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>30.76</v>
+        <v>24.3498</v>
       </c>
       <c r="I14" t="n">
-        <v>-35.8466</v>
+        <v>-31.0784</v>
       </c>
       <c r="J14" t="n">
-        <v>38.49809999999999</v>
+        <v>38.0244</v>
       </c>
       <c r="K14" t="n">
-        <v>35.2253</v>
+        <v>35.5194</v>
       </c>
       <c r="L14" t="n">
-        <v>3.272300000000001</v>
+        <v>2.505499999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-43.58410000000001</v>
+        <v>-44.753</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4655</v>
+        <v>-11.1697</v>
       </c>
       <c r="O14" t="n">
-        <v>-39.1191</v>
+        <v>-33.5838</v>
       </c>
       <c r="P14" t="n">
-        <v>4.679500000000001</v>
+        <v>5.8019</v>
       </c>
       <c r="Q14" t="n">
-        <v>-26.9069</v>
+        <v>-27.8487</v>
       </c>
       <c r="R14" t="n">
-        <v>31.5857</v>
+        <v>33.65020000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>26.0444</v>
+        <v>19.5565</v>
       </c>
       <c r="T14" t="n">
-        <v>9.798799999999998</v>
+        <v>2.0906</v>
       </c>
       <c r="U14" t="n">
-        <v>16.2453</v>
+        <v>17.466</v>
       </c>
       <c r="V14" t="n">
-        <v>10.388</v>
+        <v>9.957499999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>28.4884</v>
+        <v>32.9461</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.1002</v>
+        <v>-22.9887</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6137</v>
+        <v>11.5593</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7542</v>
+        <v>11.5245</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1405000000000002</v>
+        <v>0.03490000000000015</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6879</v>
+        <v>3.6671</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3614</v>
+        <v>3.3373</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3266</v>
+        <v>0.3297999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.593599999999999</v>
+        <v>6.4287</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9722</v>
+        <v>3.8668</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6214</v>
+        <v>2.5619</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9056</v>
+        <v>-2.7617</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6108</v>
+        <v>-0.5296</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2949</v>
+        <v>-2.2321</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6962</v>
+        <v>0.7013</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3208</v>
+        <v>-2.3376</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0169</v>
+        <v>3.039</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5882</v>
+        <v>1.5962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0912</v>
+        <v>0.106</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4971</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.6412</v>
+        <v>5.594799999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>7.3901</v>
+        <v>7.327299999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7489</v>
+        <v>-1.7325</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.095600000000001</v>
+        <v>9.069699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8717</v>
+        <v>10.6601</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7761</v>
+        <v>-1.5903</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.895</v>
+        <v>-0.9274</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4318</v>
+        <v>0.3719</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3268</v>
+        <v>-1.2994</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7722</v>
+        <v>3.5938</v>
       </c>
       <c r="K3" t="n">
-        <v>2.027</v>
+        <v>1.8921</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7453</v>
+        <v>1.7016</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.6672</v>
+        <v>-4.5212</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5952</v>
+        <v>-1.5202</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.072</v>
+        <v>-3.001</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7131</v>
+        <v>3.7403</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7131</v>
+        <v>3.7403</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4547</v>
+        <v>1.4647</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.007900000000000035</v>
+        <v>0.009099999999999997</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4627</v>
+        <v>1.4556</v>
       </c>
       <c r="V3" t="n">
-        <v>4.822699999999999</v>
+        <v>4.792199999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1074</v>
+        <v>7.0572</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2848</v>
+        <v>-2.265</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8.040800000000001</v>
+        <v>7.9759</v>
       </c>
       <c r="E4" t="n">
-        <v>9.966000000000001</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9252</v>
+        <v>-1.676</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9285</v>
+        <v>1.8813</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6221</v>
+        <v>7.5582</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.6937</v>
+        <v>-5.6769</v>
       </c>
       <c r="J4" t="n">
-        <v>10.0549</v>
+        <v>9.7903</v>
       </c>
       <c r="K4" t="n">
-        <v>9.772300000000001</v>
+        <v>9.591999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2826999999999997</v>
+        <v>0.1983999999999995</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.1265</v>
+        <v>-7.909</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1501</v>
+        <v>-2.0337</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.9763</v>
+        <v>-5.8754</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2321</v>
+        <v>0.2338</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.4093</v>
+        <v>-4.4415</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6414</v>
+        <v>4.6753</v>
       </c>
       <c r="S4" t="n">
-        <v>1.988</v>
+        <v>1.9985</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2492</v>
+        <v>-0.2266999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2371</v>
+        <v>2.2251</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8923</v>
+        <v>3.8623</v>
       </c>
       <c r="W4" t="n">
-        <v>4.5694</v>
+        <v>4.5299</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6772</v>
+        <v>-0.6676</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7555</v>
+        <v>3.8104</v>
       </c>
       <c r="E5" t="n">
-        <v>6.523300000000001</v>
+        <v>6.4297</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.7678</v>
+        <v>-2.6193</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6661</v>
+        <v>1.6944</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6917</v>
+        <v>2.7201</v>
       </c>
       <c r="I5" t="n">
         <v>-1.0256</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9893</v>
+        <v>2.9102</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2746</v>
+        <v>3.2416</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2852000000000001</v>
+        <v>-0.3314</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3233</v>
+        <v>-1.2157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5829</v>
+        <v>-0.5215000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.6942</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6246</v>
+        <v>1.6364</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6246</v>
+        <v>1.6364</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5367</v>
+        <v>1.5446</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1775</v>
+        <v>0.1896</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3593</v>
+        <v>1.355</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3564</v>
+        <v>3.3299</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.428100000000001</v>
+        <v>-4.3948</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.616</v>
+        <v>3.5972</v>
       </c>
       <c r="E6" t="n">
-        <v>4.680800000000001</v>
+        <v>4.5303</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0649</v>
+        <v>-0.9331</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1338</v>
+        <v>2.1005</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5227</v>
+        <v>3.4544</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3889</v>
+        <v>-1.354</v>
       </c>
       <c r="J6" t="n">
-        <v>3.611</v>
+        <v>3.478499999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2799</v>
+        <v>3.1488</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3312</v>
+        <v>0.3295</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4772</v>
+        <v>-1.3779</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2428</v>
+        <v>0.3057</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.72</v>
+        <v>-1.6836</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2321</v>
+        <v>0.2338</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6246</v>
+        <v>-1.6364</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8565</v>
+        <v>1.8701</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7859</v>
+        <v>1.7955</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4095</v>
+        <v>0.4233</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3764</v>
+        <v>1.3721</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5357999999999998</v>
+        <v>-0.5323999999999998</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2847</v>
+        <v>2.265</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8206</v>
+        <v>-2.7974</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4154</v>
+        <v>3.428400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1293</v>
+        <v>4.0646</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7139</v>
+        <v>-0.6361999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6466</v>
+        <v>3.6502</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0208</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6258</v>
+        <v>1.6302</v>
       </c>
       <c r="J7" t="n">
-        <v>4.776400000000001</v>
+        <v>4.7121</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5758</v>
+        <v>2.5334</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2007</v>
+        <v>2.1787</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1298</v>
+        <v>-1.0619</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5551</v>
+        <v>-0.5135000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5748</v>
+        <v>-0.5484</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4642</v>
+        <v>0.4676</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4641</v>
+        <v>-0.4675</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9283</v>
+        <v>0.9351</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3764</v>
+        <v>0.3756</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.183</v>
+        <v>-0.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5594</v>
+        <v>0.5557000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2.154</v>
+        <v>2.211</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8466</v>
+        <v>0.7738</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3075</v>
+        <v>1.4371</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5183</v>
+        <v>-1.4797</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4087000000000001</v>
+        <v>0.4241000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9271</v>
+        <v>-1.9039</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7501000000000002</v>
+        <v>0.6711</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.4523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2435999999999999</v>
+        <v>0.2188</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2684</v>
+        <v>-2.1509</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0978</v>
+        <v>-0.0282</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1707</v>
+        <v>-2.1227</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3925</v>
+        <v>1.4027</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6963</v>
+        <v>-0.7014</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0886</v>
+        <v>2.1038</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3496</v>
+        <v>1.3582</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2567</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0928</v>
+        <v>1.0868</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9304000000000001</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5359</v>
+        <v>0.5325</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3945</v>
+        <v>0.3974</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3378</v>
+        <v>1.3506</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0016</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3362</v>
+        <v>1.3496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7188</v>
+        <v>0.7281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3555</v>
+        <v>0.3617</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3633</v>
+        <v>0.3664</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0704</v>
+        <v>0.0699</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0336</v>
+        <v>0.0332</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6484</v>
+        <v>0.6582</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3219</v>
+        <v>0.3284</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3265</v>
+        <v>0.3298</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4641</v>
+        <v>0.4675</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4641</v>
+        <v>0.4675</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1548</v>
+        <v>0.155</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0688</v>
+        <v>-0.0689</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2236</v>
+        <v>0.2238</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1503</v>
+        <v>1.2472</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1878</v>
+        <v>5.1233</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0376</v>
+        <v>-3.8762</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3874</v>
+        <v>-0.3208000000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0983</v>
+        <v>2.113</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4857</v>
+        <v>-2.4339</v>
       </c>
       <c r="J10" t="n">
-        <v>3.27</v>
+        <v>3.222</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0124</v>
+        <v>2.9657</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2576</v>
+        <v>0.2563</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6574</v>
+        <v>-3.543</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9141</v>
+        <v>-0.8526</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.7433</v>
+        <v>-2.6903</v>
       </c>
       <c r="P10" t="n">
         <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6245</v>
+        <v>-1.6364</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6244</v>
+        <v>1.6363</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7508</v>
+        <v>2.7682</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1163</v>
+        <v>1.1376</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6344</v>
+        <v>1.6304</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.213</v>
+        <v>-1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4261</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.639</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4677999999999999</v>
+        <v>-0.4766000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2596000000000001</v>
+        <v>-0.4964999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2079999999999997</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5136</v>
+        <v>-5.5301</v>
       </c>
       <c r="H11" t="n">
-        <v>1.599</v>
+        <v>1.5567</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.1125</v>
+        <v>-7.0869</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4068999999999998</v>
+        <v>-0.6172</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7322</v>
+        <v>2.5903</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1391</v>
+        <v>-3.2076</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.1066</v>
+        <v>-4.9129</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1333</v>
+        <v>-1.0337</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.9735</v>
+        <v>-3.8793</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8566</v>
+        <v>1.8702</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5528</v>
+        <v>-2.5714</v>
       </c>
       <c r="R11" t="n">
-        <v>4.4093</v>
+        <v>4.4416</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3708</v>
+        <v>2.3808</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.262</v>
+        <v>-0.2403</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6327</v>
+        <v>2.6212</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8184000000000002</v>
+        <v>0.8026</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9619</v>
+        <v>2.9325</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1434</v>
+        <v>-2.1299</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.438</v>
+        <v>-2.4094</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2578</v>
+        <v>-1.471</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1802</v>
+        <v>-0.9382999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.596499999999999</v>
+        <v>-8.57</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.174</v>
+        <v>-2.2173</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.4226</v>
+        <v>-6.3527</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.516</v>
+        <v>-0.6987</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4614</v>
+        <v>0.3097</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9774</v>
+        <v>-1.0085</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.080500000000001</v>
+        <v>-7.8713</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.6353</v>
+        <v>-2.5271</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.4452</v>
+        <v>-5.3442</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1604</v>
+        <v>1.1688</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9452</v>
+        <v>-3.9741</v>
       </c>
       <c r="R12" t="n">
-        <v>5.1056</v>
+        <v>5.1428</v>
       </c>
       <c r="S12" t="n">
-        <v>2.572</v>
+        <v>2.5917</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6361000000000001</v>
+        <v>0.6665999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.936</v>
+        <v>1.9252</v>
       </c>
       <c r="V12" t="n">
-        <v>2.4261</v>
+        <v>2.4</v>
       </c>
       <c r="W12" t="n">
-        <v>2.567400000000001</v>
+        <v>2.5351</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.6861</v>
+        <v>-12.7339</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.2307</v>
+        <v>-7.5201</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.4554</v>
+        <v>-5.2138</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.599499999999999</v>
+        <v>-3.6414</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4118</v>
+        <v>2.4037</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0112</v>
+        <v>-6.0452</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0594</v>
+        <v>2.8284</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8715</v>
+        <v>3.7672</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8121000000000003</v>
+        <v>-0.9388000000000003</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6589</v>
+        <v>-6.4699</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4598</v>
+        <v>-1.3634</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1992</v>
+        <v>-5.1065</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.033899999999999</v>
+        <v>-6.0779</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2111</v>
+        <v>-10.2857</v>
       </c>
       <c r="R13" t="n">
-        <v>4.1774</v>
+        <v>4.2077</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6286</v>
+        <v>1.6427</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1741999999999999</v>
+        <v>0.1995</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4545</v>
+        <v>1.443</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6814</v>
+        <v>-4.6571</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2532</v>
+        <v>-0.2623</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.4282</v>
+        <v>-4.3948</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>28.58720000000001</v>
+        <v>28.62980000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>45.2132</v>
+        <v>43.27170000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.6259</v>
+        <v>-14.6416</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.728599999999997</v>
+        <v>-6.747800000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>24.3498</v>
+        <v>24.1038</v>
       </c>
       <c r="I14" t="n">
-        <v>-31.0784</v>
+        <v>-30.8521</v>
       </c>
       <c r="J14" t="n">
-        <v>38.0244</v>
+        <v>36.3891</v>
       </c>
       <c r="K14" t="n">
-        <v>35.5194</v>
+        <v>34.3931</v>
       </c>
       <c r="L14" t="n">
-        <v>2.505499999999999</v>
+        <v>1.995499999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-44.753</v>
+        <v>-43.13720000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.1697</v>
+        <v>-10.2894</v>
       </c>
       <c r="O14" t="n">
-        <v>-33.5838</v>
+        <v>-32.8479</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8019</v>
+        <v>5.8444</v>
       </c>
       <c r="Q14" t="n">
-        <v>-27.8487</v>
+        <v>-28.052</v>
       </c>
       <c r="R14" t="n">
-        <v>33.65020000000001</v>
+        <v>33.8959</v>
       </c>
       <c r="S14" t="n">
-        <v>19.5565</v>
+        <v>19.6717</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0906</v>
+        <v>2.2873</v>
       </c>
       <c r="U14" t="n">
-        <v>17.466</v>
+        <v>17.3839</v>
       </c>
       <c r="V14" t="n">
-        <v>9.957499999999998</v>
+        <v>9.862500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>32.9461</v>
+        <v>32.64709999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.9887</v>
+        <v>-22.7846</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5593</v>
+        <v>11.5553</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5245</v>
+        <v>11.5029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03490000000000015</v>
+        <v>0.0522999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6671</v>
+        <v>3.6623</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3373</v>
+        <v>3.3332</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3297999999999999</v>
+        <v>0.3290999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4287</v>
+        <v>6.4307</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8668</v>
+        <v>3.8654</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5619</v>
+        <v>2.5653</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7617</v>
+        <v>-2.7684</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5296</v>
+        <v>-0.5321</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2321</v>
+        <v>-2.2362</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7013</v>
+        <v>0.7018</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3376</v>
+        <v>-2.3394</v>
       </c>
       <c r="R2" t="n">
-        <v>3.039</v>
+        <v>3.0413</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5962</v>
+        <v>1.6013</v>
       </c>
       <c r="T2" t="n">
-        <v>0.106</v>
+        <v>0.0912</v>
       </c>
       <c r="U2" t="n">
-        <v>1.49</v>
+        <v>1.5101</v>
       </c>
       <c r="V2" t="n">
-        <v>5.594799999999999</v>
+        <v>5.589799999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>7.327299999999999</v>
+        <v>7.3205</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7325</v>
+        <v>-1.7307</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.069699999999999</v>
+        <v>9.0718</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6601</v>
+        <v>10.6422</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5903</v>
+        <v>-1.5704</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9274</v>
+        <v>-0.927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3719</v>
+        <v>0.3739</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2994</v>
+        <v>-1.3008</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5938</v>
+        <v>3.5992</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8921</v>
+        <v>1.8949</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7016</v>
+        <v>1.7043</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.5212</v>
+        <v>-4.5262</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5202</v>
+        <v>-1.5211</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.001</v>
+        <v>-3.0052</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7403</v>
+        <v>3.7431</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7403</v>
+        <v>3.7431</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4647</v>
+        <v>1.4665</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009099999999999997</v>
+        <v>-0.008700000000000024</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4556</v>
+        <v>1.4755</v>
       </c>
       <c r="V3" t="n">
-        <v>4.792199999999999</v>
+        <v>4.7889</v>
       </c>
       <c r="W3" t="n">
-        <v>7.0572</v>
+        <v>7.0517</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.265</v>
+        <v>-2.2628</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9759</v>
+        <v>7.9735</v>
       </c>
       <c r="E4" t="n">
-        <v>9.651999999999999</v>
+        <v>9.6197</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.676</v>
+        <v>-1.6462</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8813</v>
+        <v>1.876200000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5582</v>
+        <v>7.5495</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.6769</v>
+        <v>-5.673300000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9.7903</v>
+        <v>9.791399999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>9.591999999999999</v>
+        <v>9.584900000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1983999999999995</v>
+        <v>0.2066000000000003</v>
       </c>
       <c r="M4" t="n">
-        <v>-7.909</v>
+        <v>-7.9153</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0337</v>
+        <v>-2.0355</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.8754</v>
+        <v>-5.879799999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.4415</v>
+        <v>-4.445</v>
       </c>
       <c r="R4" t="n">
-        <v>4.6753</v>
+        <v>4.678900000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9985</v>
+        <v>2.0042</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2266999999999999</v>
+        <v>-0.2523</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2251</v>
+        <v>2.2567</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8623</v>
+        <v>3.8591</v>
       </c>
       <c r="W4" t="n">
-        <v>4.5299</v>
+        <v>4.525600000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6676</v>
+        <v>-0.6665</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8104</v>
+        <v>3.8128</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4297</v>
+        <v>6.4169</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6193</v>
+        <v>-2.6041</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6944</v>
+        <v>1.6901</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7201</v>
+        <v>2.7147</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0256</v>
+        <v>-1.0246</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9102</v>
+        <v>2.9115</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2416</v>
+        <v>3.238</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3314</v>
+        <v>-0.3265000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2157</v>
+        <v>-1.2215</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5215000000000001</v>
+        <v>-0.5232</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6942</v>
+        <v>-0.6982</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6364</v>
+        <v>1.6375</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6364</v>
+        <v>1.6375</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5446</v>
+        <v>1.5493</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1896</v>
+        <v>0.1783999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.355</v>
+        <v>1.3709</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3299</v>
+        <v>3.327</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.3948</v>
+        <v>-4.3912</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5972</v>
+        <v>3.5983</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5303</v>
+        <v>4.516400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9331</v>
+        <v>-0.9181</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1005</v>
+        <v>2.0959</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4544</v>
+        <v>3.452</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.354</v>
+        <v>-1.3561</v>
       </c>
       <c r="J6" t="n">
-        <v>3.478499999999999</v>
+        <v>3.479</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1488</v>
+        <v>3.1494</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3295</v>
+        <v>0.3294</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3779</v>
+        <v>-1.3831</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3057</v>
+        <v>0.3026</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6836</v>
+        <v>-1.6856</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6364</v>
+        <v>-1.6375</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8701</v>
+        <v>1.8716</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7955</v>
+        <v>1.8006</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4233</v>
+        <v>0.4123</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3721</v>
+        <v>1.3883</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5323999999999998</v>
+        <v>-0.5321</v>
       </c>
       <c r="W6" t="n">
-        <v>2.265</v>
+        <v>2.2628</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7974</v>
+        <v>-2.7949</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.428400000000001</v>
+        <v>3.4284</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0646</v>
+        <v>4.0575</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6361999999999999</v>
+        <v>-0.6291</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6502</v>
+        <v>3.6451</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>2.017</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6302</v>
+        <v>1.6282</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7121</v>
+        <v>4.7101</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5334</v>
+        <v>2.5313</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1787</v>
+        <v>2.1788</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0619</v>
+        <v>-1.065</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5135000000000001</v>
+        <v>-0.5144</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5484</v>
+        <v>-0.5506</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4676</v>
+        <v>0.4678</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4675</v>
+        <v>-0.4679</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9351</v>
+        <v>0.9357</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3756</v>
+        <v>0.3795</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.18</v>
+        <v>-0.1847</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5557000000000001</v>
+        <v>0.5642</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2.211</v>
+        <v>2.2125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7738</v>
+        <v>0.7635000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4371</v>
+        <v>1.449</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4797</v>
+        <v>-1.4815</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4241000000000001</v>
+        <v>0.4228000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9039</v>
+        <v>-1.9043</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6711</v>
+        <v>0.675</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4523</v>
+        <v>0.4539</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2188</v>
+        <v>0.2211000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1509</v>
+        <v>-2.1565</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0282</v>
+        <v>-0.03099999999999997</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1227</v>
+        <v>-2.1255</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4027</v>
+        <v>1.4036</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.7014</v>
+        <v>-0.7017</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1038</v>
+        <v>2.1055</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3582</v>
+        <v>1.3604</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2715</v>
+        <v>0.2582</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0868</v>
+        <v>1.1023</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9298</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5325</v>
+        <v>0.5321</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3974</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="9">
@@ -1114,22 +1114,22 @@
         <v>1.3506</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001</v>
+        <v>0.0004</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3496</v>
+        <v>1.3502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7281</v>
+        <v>0.7266</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3617</v>
+        <v>0.3609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3664</v>
+        <v>0.3658</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0699</v>
+        <v>0.0698</v>
       </c>
       <c r="K9" t="n">
         <v>0.0332</v>
@@ -1138,31 +1138,31 @@
         <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6582</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3284</v>
+        <v>0.3277</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3298</v>
+        <v>0.3291</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="S9" t="n">
-        <v>0.155</v>
+        <v>0.1561</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0689</v>
+        <v>-0.0694</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2238</v>
+        <v>0.2255</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2472</v>
+        <v>1.2469</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1233</v>
+        <v>5.1035</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8762</v>
+        <v>-3.8565</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3208000000000002</v>
+        <v>-0.3275999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.113</v>
+        <v>2.1091</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4339</v>
+        <v>-2.4367</v>
       </c>
       <c r="J10" t="n">
-        <v>3.222</v>
+        <v>3.2194</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9657</v>
+        <v>2.9632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2563</v>
+        <v>0.2562</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.543</v>
+        <v>-3.5469</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8526</v>
+        <v>-0.8539</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6903</v>
+        <v>-2.693</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6364</v>
+        <v>-1.6376</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6363</v>
+        <v>1.6376</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7682</v>
+        <v>2.7731</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1376</v>
+        <v>1.1247</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6304</v>
+        <v>1.6485</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2</v>
+        <v>-1.1986</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.3972</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.6</v>
+        <v>-3.595800000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4766000000000001</v>
+        <v>-0.4638</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4964999999999999</v>
+        <v>-0.5148999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01999999999999957</v>
+        <v>0.05100000000000016</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5301</v>
+        <v>-5.5266</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5567</v>
+        <v>1.5561</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.0869</v>
+        <v>-7.0827</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6172</v>
+        <v>-0.6053999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5903</v>
+        <v>2.5924</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.2076</v>
+        <v>-3.1977</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.9129</v>
+        <v>-4.921099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0337</v>
+        <v>-1.0363</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.8793</v>
+        <v>-3.885</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8702</v>
+        <v>1.8715</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5714</v>
+        <v>-2.5734</v>
       </c>
       <c r="R11" t="n">
-        <v>4.4416</v>
+        <v>4.444900000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3808</v>
+        <v>2.3903</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2403</v>
+        <v>-0.2653</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6212</v>
+        <v>2.6555</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8026</v>
+        <v>0.8009000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9325</v>
+        <v>2.9293</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1299</v>
+        <v>-2.1284</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4094</v>
+        <v>-2.406</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.471</v>
+        <v>-1.4944</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9382999999999999</v>
+        <v>-0.9114</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.57</v>
+        <v>-8.5657</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2173</v>
+        <v>-2.2121</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.3527</v>
+        <v>-6.3535</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6987</v>
+        <v>-0.6887000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3097</v>
+        <v>0.3156</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0085</v>
+        <v>-1.0044</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.8713</v>
+        <v>-7.8768</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5271</v>
+        <v>-2.5277</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.3442</v>
+        <v>-5.3491</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1688</v>
+        <v>1.1698</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9741</v>
+        <v>-3.9771</v>
       </c>
       <c r="R12" t="n">
-        <v>5.1428</v>
+        <v>5.1468</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5917</v>
+        <v>2.5928</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6665999999999999</v>
+        <v>0.6398</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9252</v>
+        <v>1.953</v>
       </c>
       <c r="V12" t="n">
-        <v>2.4</v>
+        <v>2.3972</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5351</v>
+        <v>2.5316</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.7339</v>
+        <v>-12.7311</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.5201</v>
+        <v>-7.5421</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.2138</v>
+        <v>-5.189</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6414</v>
+        <v>-3.6356</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4037</v>
+        <v>2.4004</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0452</v>
+        <v>-6.0359</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8284</v>
+        <v>2.8406</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7672</v>
+        <v>3.7657</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9388000000000003</v>
+        <v>-0.9251000000000003</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.4699</v>
+        <v>-6.4762</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3634</v>
+        <v>-1.3654</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1065</v>
+        <v>-5.1108</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.0779</v>
+        <v>-6.0827</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2857</v>
+        <v>-10.2938</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2077</v>
+        <v>4.211</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6427</v>
+        <v>1.6416</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1995</v>
+        <v>0.1744000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.443</v>
+        <v>1.4672</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6571</v>
+        <v>-4.654500000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2623</v>
+        <v>-0.2633</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3948</v>
+        <v>-4.3912</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>28.62980000000001</v>
+        <v>28.64919999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>43.27170000000001</v>
+        <v>43.07160000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.6416</v>
+        <v>-14.4223</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.747800000000002</v>
+        <v>-6.767799999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>24.1038</v>
+        <v>24.0775</v>
       </c>
       <c r="I14" t="n">
-        <v>-30.8521</v>
+        <v>-30.8448</v>
       </c>
       <c r="J14" t="n">
-        <v>36.3891</v>
+        <v>36.4326</v>
       </c>
       <c r="K14" t="n">
-        <v>34.3931</v>
+        <v>34.38789999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.995499999999999</v>
+        <v>2.044600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-43.13720000000001</v>
+        <v>-43.2002</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.2894</v>
+        <v>-10.3103</v>
       </c>
       <c r="O14" t="n">
-        <v>-32.8479</v>
+        <v>-32.8899</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8444</v>
+        <v>5.8481</v>
       </c>
       <c r="Q14" t="n">
-        <v>-28.052</v>
+        <v>-28.0734</v>
       </c>
       <c r="R14" t="n">
-        <v>33.8959</v>
+        <v>33.9218</v>
       </c>
       <c r="S14" t="n">
-        <v>19.6717</v>
+        <v>19.7157</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2873</v>
+        <v>2.0986</v>
       </c>
       <c r="U14" t="n">
-        <v>17.3839</v>
+        <v>17.6177</v>
       </c>
       <c r="V14" t="n">
-        <v>9.862500000000001</v>
+        <v>9.852099999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>32.64709999999999</v>
+        <v>32.6145</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.7846</v>
+        <v>-22.7624</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Real Madrid.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5553</v>
+        <v>11.5551</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5029</v>
+        <v>11.5016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0522999999999999</v>
+        <v>0.05359999999999987</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6623</v>
+        <v>3.6617</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3332</v>
+        <v>3.3327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3290999999999999</v>
+        <v>0.3289</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4307</v>
+        <v>6.4332</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8654</v>
+        <v>3.8664</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5653</v>
+        <v>2.5668</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7684</v>
+        <v>-2.7714</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5321</v>
+        <v>-0.5337</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2362</v>
+        <v>-2.2378</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7018</v>
+        <v>0.7019</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3394</v>
+        <v>-2.3396</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0413</v>
+        <v>3.0416</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6013</v>
+        <v>1.6022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0912</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5101</v>
+        <v>1.5141</v>
       </c>
       <c r="V2" t="n">
-        <v>5.589799999999999</v>
+        <v>5.589499999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>7.3205</v>
+        <v>7.32</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7307</v>
+        <v>-1.7305</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +631,67 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9.0718</v>
+        <v>9.0724</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6422</v>
+        <v>10.6414</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5704</v>
+        <v>-1.569</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.927</v>
+        <v>-0.9265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3739</v>
+        <v>0.3749</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3008</v>
+        <v>-1.3015</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5992</v>
+        <v>3.6026</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8949</v>
+        <v>1.8972</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7043</v>
+        <v>1.7054</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.5262</v>
+        <v>-4.5291</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5211</v>
+        <v>-1.5221</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.0052</v>
+        <v>-3.0069</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7431</v>
+        <v>3.7434</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7431</v>
+        <v>3.7434</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4665</v>
+        <v>1.4669</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.008700000000000024</v>
+        <v>-0.01239999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4755</v>
+        <v>1.4793</v>
       </c>
       <c r="V3" t="n">
-        <v>4.7889</v>
+        <v>4.7887</v>
       </c>
       <c r="W3" t="n">
-        <v>7.0517</v>
+        <v>7.051299999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2628</v>
+        <v>-2.2627</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +709,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9735</v>
+        <v>7.9738</v>
       </c>
       <c r="E4" t="n">
-        <v>9.6197</v>
+        <v>9.6173</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6462</v>
+        <v>-1.6434</v>
       </c>
       <c r="G4" t="n">
-        <v>1.876200000000001</v>
+        <v>1.875800000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5495</v>
+        <v>7.5485</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.673300000000001</v>
+        <v>-5.672699999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.791399999999999</v>
+        <v>9.795</v>
       </c>
       <c r="K4" t="n">
-        <v>9.584900000000001</v>
+        <v>9.585799999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2066000000000003</v>
+        <v>0.2092000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-7.9153</v>
+        <v>-7.9191</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0355</v>
+        <v>-2.0372</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.879799999999999</v>
+        <v>-5.8819</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.445</v>
+        <v>-4.4453</v>
       </c>
       <c r="R4" t="n">
-        <v>4.678900000000001</v>
+        <v>4.6793</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0042</v>
+        <v>2.0053</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2523</v>
+        <v>-0.2575999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2567</v>
+        <v>2.2629</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8591</v>
+        <v>3.8588</v>
       </c>
       <c r="W4" t="n">
-        <v>4.525600000000001</v>
+        <v>4.5252</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6665</v>
+        <v>-0.6664</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +787,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8128</v>
+        <v>3.8126</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4169</v>
+        <v>6.415699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6041</v>
+        <v>-2.603</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6901</v>
+        <v>1.6889</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7147</v>
+        <v>2.7133</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0246</v>
+        <v>-1.0245</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9115</v>
+        <v>2.9128</v>
       </c>
       <c r="K5" t="n">
-        <v>3.238</v>
+        <v>3.2377</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3265000000000001</v>
+        <v>-0.3249000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2215</v>
+        <v>-1.2239</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5232</v>
+        <v>-0.5244</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6982</v>
+        <v>-0.6996</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6375</v>
+        <v>1.6378</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6375</v>
+        <v>1.6378</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5493</v>
+        <v>1.5501</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1783999999999999</v>
+        <v>0.1761</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3709</v>
+        <v>1.3742</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
       <c r="W5" t="n">
-        <v>3.327</v>
+        <v>3.3268</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.3912</v>
+        <v>-4.3909</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +865,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5983</v>
+        <v>3.5987</v>
       </c>
       <c r="E6" t="n">
-        <v>4.516400000000001</v>
+        <v>4.5156</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9181</v>
+        <v>-0.9168999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0959</v>
+        <v>2.0954</v>
       </c>
       <c r="H6" t="n">
-        <v>3.452</v>
+        <v>3.4524</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3561</v>
+        <v>-1.357</v>
       </c>
       <c r="J6" t="n">
-        <v>3.479</v>
+        <v>3.4807</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1494</v>
+        <v>3.1513</v>
       </c>
       <c r="L6" t="n">
         <v>0.3294</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3831</v>
+        <v>-1.3853</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3026</v>
+        <v>0.3012</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6856</v>
+        <v>-1.6864</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.6375</v>
+        <v>-1.6378</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8716</v>
+        <v>1.8717</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8006</v>
+        <v>1.8015</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4123</v>
+        <v>0.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3883</v>
+        <v>1.3914</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5321</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2628</v>
+        <v>2.2626</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7949</v>
+        <v>-2.7947</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +943,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4284</v>
+        <v>3.4282</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0575</v>
+        <v>4.0569</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6291</v>
+        <v>-0.6288</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6451</v>
+        <v>3.6442</v>
       </c>
       <c r="H7" t="n">
-        <v>2.017</v>
+        <v>2.0164</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6282</v>
+        <v>1.6277</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7101</v>
+        <v>4.7105</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5313</v>
+        <v>2.5314</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1788</v>
+        <v>2.1791</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.065</v>
+        <v>-1.0663</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5144</v>
+        <v>-0.5150999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5506</v>
+        <v>-0.5514</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4678</v>
+        <v>0.468</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.4679</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9357</v>
+        <v>0.9359</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3795</v>
+        <v>0.3803</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1847</v>
+        <v>-0.1857</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5642</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1021,58 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2125</v>
+        <v>2.2121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7635000000000001</v>
+        <v>0.7624</v>
       </c>
       <c r="F8" t="n">
-        <v>1.449</v>
+        <v>1.4496</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4815</v>
+        <v>-1.4823</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4228000000000001</v>
+        <v>0.4224999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9043</v>
+        <v>-1.9047</v>
       </c>
       <c r="J8" t="n">
-        <v>0.675</v>
+        <v>0.6767999999999998</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4539</v>
+        <v>0.4549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2211000000000001</v>
+        <v>0.2219000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1565</v>
+        <v>-2.1591</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03099999999999997</v>
+        <v>-0.03240000000000004</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1255</v>
+        <v>-2.1266</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4036</v>
+        <v>1.4039</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.7017</v>
+        <v>-0.7020000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1055</v>
+        <v>2.1056</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3604</v>
+        <v>1.3609</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2582</v>
+        <v>0.2554999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1023</v>
+        <v>1.1054</v>
       </c>
       <c r="V8" t="n">
         <v>0.9298</v>
@@ -1111,22 +1099,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3506</v>
+        <v>1.3505</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3502</v>
+        <v>1.3501</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7266</v>
+        <v>0.7262</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3609</v>
+        <v>0.3606</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3658</v>
+        <v>0.3656</v>
       </c>
       <c r="J9" t="n">
         <v>0.0698</v>
@@ -1138,13 +1126,13 @@
         <v>0.0366</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3277</v>
+        <v>0.3274</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3291</v>
+        <v>0.329</v>
       </c>
       <c r="P9" t="n">
         <v>0.4679</v>
@@ -1156,13 +1144,13 @@
         <v>0.4679</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1561</v>
+        <v>0.1563</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0694</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2255</v>
+        <v>0.2258</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1177,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2469</v>
+        <v>1.2457</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1035</v>
+        <v>5.1005</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8565</v>
+        <v>-3.8549</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3275999999999999</v>
+        <v>-0.3297000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1091</v>
+        <v>2.1083</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4367</v>
+        <v>-2.4379</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2194</v>
+        <v>3.2195</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9632</v>
+        <v>2.9633</v>
       </c>
       <c r="L10" t="n">
         <v>0.2562</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5469</v>
+        <v>-3.5491</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8539</v>
+        <v>-0.8549</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.693</v>
+        <v>-2.6941</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6376</v>
+        <v>-1.6378</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6376</v>
+        <v>1.6377</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7731</v>
+        <v>2.7738</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1247</v>
+        <v>1.1218</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6485</v>
+        <v>1.6519</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1986</v>
+        <v>-1.1984</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3972</v>
+        <v>2.3969</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.595800000000001</v>
+        <v>-3.595499999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1255,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4638</v>
+        <v>-0.4611</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5148999999999999</v>
+        <v>-0.5154000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05100000000000016</v>
+        <v>0.0541999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5266</v>
+        <v>-5.5256</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5561</v>
+        <v>1.5565</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.0827</v>
+        <v>-7.082100000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6053999999999999</v>
+        <v>-0.6004</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5924</v>
+        <v>2.5944</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1977</v>
+        <v>-3.195</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.921099999999999</v>
+        <v>-4.9252</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0363</v>
+        <v>-1.0379</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.885</v>
+        <v>-3.8871</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8715</v>
+        <v>1.8717</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5734</v>
+        <v>-2.5736</v>
       </c>
       <c r="R11" t="n">
-        <v>4.444900000000001</v>
+        <v>4.4453</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3903</v>
+        <v>2.3919</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2653</v>
+        <v>-0.2704</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6555</v>
+        <v>2.6624</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8009000000000002</v>
+        <v>0.8007999999999997</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9293</v>
+        <v>2.9291</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1284</v>
+        <v>-2.1283</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1333,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.406</v>
+        <v>-2.4056</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4944</v>
+        <v>-1.4964</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9114</v>
+        <v>-0.9093</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.5657</v>
+        <v>-8.565200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2121</v>
+        <v>-2.2105</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.3535</v>
+        <v>-6.3545</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6887000000000001</v>
+        <v>-0.6846</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3156</v>
+        <v>0.3186</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0044</v>
+        <v>-1.0032</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.8768</v>
+        <v>-7.8805</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5277</v>
+        <v>-2.5291</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.3491</v>
+        <v>-5.3513</v>
       </c>
       <c r="P12" t="n">
         <v>1.1698</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9771</v>
+        <v>-3.9774</v>
       </c>
       <c r="R12" t="n">
-        <v>5.1468</v>
+        <v>5.1472</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5928</v>
+        <v>2.5927</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6398</v>
+        <v>0.6342000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.953</v>
+        <v>1.9585</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3972</v>
+        <v>2.397</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5316</v>
+        <v>2.5313</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1411,67 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.7311</v>
+        <v>-12.7299</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.5421</v>
+        <v>-7.542900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.189</v>
+        <v>-5.187099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6356</v>
+        <v>-3.634</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4004</v>
+        <v>2.3998</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0359</v>
+        <v>-6.033700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8406</v>
+        <v>2.8458</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7657</v>
+        <v>3.7667</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9251000000000003</v>
+        <v>-0.9209999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.4762</v>
+        <v>-6.4797</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3654</v>
+        <v>-1.3669</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1108</v>
+        <v>-5.1127</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.0827</v>
+        <v>-6.082999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2938</v>
+        <v>-10.2943</v>
       </c>
       <c r="R13" t="n">
-        <v>4.211</v>
+        <v>4.2113</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6416</v>
+        <v>1.6414</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1744000000000001</v>
+        <v>0.1691000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4672</v>
+        <v>1.4722</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.654500000000001</v>
+        <v>-4.6543</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2633</v>
+        <v>-0.2634</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3912</v>
+        <v>-4.3909</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>28.64919999999999</v>
+        <v>28.65249999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>43.07160000000001</v>
+        <v>43.057</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.4223</v>
+        <v>-14.4049</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.767799999999999</v>
+        <v>-6.771100000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>24.0775</v>
+        <v>24.0754</v>
       </c>
       <c r="I14" t="n">
-        <v>-30.8448</v>
+        <v>-30.8464</v>
       </c>
       <c r="J14" t="n">
-        <v>36.4326</v>
+        <v>36.46169999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>34.38789999999999</v>
+        <v>34.4009</v>
       </c>
       <c r="L14" t="n">
-        <v>2.044600000000001</v>
+        <v>2.060499999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-43.2002</v>
+        <v>-43.2323</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.3103</v>
+        <v>-10.3251</v>
       </c>
       <c r="O14" t="n">
-        <v>-32.8899</v>
+        <v>-32.90679999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8481</v>
+        <v>5.849300000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-28.0734</v>
+        <v>-28.0757</v>
       </c>
       <c r="R14" t="n">
-        <v>33.9218</v>
+        <v>33.9247</v>
       </c>
       <c r="S14" t="n">
-        <v>19.7157</v>
+        <v>19.7233</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0986</v>
+        <v>2.059200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>17.6177</v>
+        <v>17.6641</v>
       </c>
       <c r="V14" t="n">
-        <v>9.852099999999998</v>
+        <v>9.851600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>32.6145</v>
+        <v>32.6119</v>
       </c>
       <c r="X14" t="n">
-        <v>-22.7624</v>
+        <v>-22.7606</v>
       </c>
     </row>
   </sheetData>
